--- a/LAB1/ZALACZNIKI/C1 ze screenami.xlsx
+++ b/LAB1/ZALACZNIKI/C1 ze screenami.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\piotr\Desktop\STUDIA\sem4\TWM\TWM_LABY_26L\LAB1\ZALACZNIKI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8BBBE80C-883A-4174-8985-1947D968FED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D00FDD3E-BC71-4939-A08C-94E04E046877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -137,9 +137,6 @@
     <t>zliczone miarką</t>
   </si>
   <si>
-    <t>zdjecie wzorca wrzucone do image viewera - stamdą wymiar</t>
-  </si>
-  <si>
     <t>wzór na Obliczona odległość do wzorca</t>
   </si>
   <si>
@@ -147,13 +144,16 @@
   </si>
   <si>
     <t>Maksymalna szybkość obiektu</t>
+  </si>
+  <si>
+    <t>zdjecie wzorca wrzucone do image viewera - stamdąd wymiar</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -197,6 +197,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="238"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
@@ -322,7 +329,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -372,9 +379,12 @@
     <xf numFmtId="2" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -398,16 +408,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>47368</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>18793</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>95909</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>73049</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>76790</xdr:rowOff>
+      <xdr:rowOff>105365</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -430,7 +440,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8924668" y="4267200"/>
+          <a:off x="10029568" y="4286250"/>
           <a:ext cx="3001291" cy="2686640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -442,16 +452,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>515109</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>534159</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>334486</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>347821</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -474,7 +484,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9392409" y="28575"/>
+          <a:off x="9173334" y="85725"/>
           <a:ext cx="5134327" cy="3648075"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -486,16 +496,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>374292</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>545742</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>182079</xdr:colOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>347814</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>72390</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -518,7 +528,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12204342" y="4276725"/>
+          <a:off x="13509267" y="4305300"/>
           <a:ext cx="5122737" cy="2638425"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -530,16 +540,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>161925</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>133351</xdr:rowOff>
+      <xdr:rowOff>123826</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>572562</xdr:colOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>496362</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>87983</xdr:rowOff>
+      <xdr:rowOff>78458</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -562,7 +572,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9039225" y="7524751"/>
+          <a:off x="10096500" y="7515226"/>
           <a:ext cx="5725587" cy="1497682"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -574,16 +584,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>76201</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>19051</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>71325</xdr:rowOff>
+      <xdr:rowOff>42750</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>561975</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>499110</xdr:colOff>
       <xdr:row>54</xdr:row>
-      <xdr:rowOff>105442</xdr:rowOff>
+      <xdr:rowOff>76867</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -606,7 +616,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8953501" y="9777300"/>
+          <a:off x="10029826" y="9748725"/>
           <a:ext cx="7572374" cy="2910667"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -907,12 +917,12 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="54.85546875" customWidth="1"/>
-    <col min="2" max="2" width="30.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -959,7 +969,7 @@
       <c r="B7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="19" t="s">
         <v>31</v>
       </c>
     </row>
@@ -970,7 +980,7 @@
       <c r="B8" s="3">
         <v>4025.3</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="19" t="s">
         <v>31</v>
       </c>
     </row>
@@ -981,7 +991,7 @@
       <c r="B9" s="3">
         <v>4024.8</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="19" t="s">
         <v>31</v>
       </c>
     </row>
@@ -992,7 +1002,7 @@
       <c r="B10" s="3">
         <v>2845.8</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="19" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1003,7 +1013,7 @@
       <c r="B11" s="3">
         <v>2148.1999999999998</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="19" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1012,6 +1022,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="2"/>
+      <c r="C12" s="19"/>
     </row>
     <row r="13" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
@@ -1020,7 +1031,7 @@
       <c r="B13" s="3">
         <v>24.2</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="19" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1031,7 +1042,7 @@
       <c r="B14" s="5">
         <v>50</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="19" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1042,8 +1053,8 @@
       <c r="B15" s="7">
         <v>2289.1356999999998</v>
       </c>
-      <c r="C15" t="s">
-        <v>34</v>
+      <c r="C15" s="19" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1054,33 +1065,33 @@
         <f>($B$8*$B$13)/B15</f>
         <v>42.554165749107838</v>
       </c>
-      <c r="C16" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C16" s="19" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B17" s="8">
         <v>100</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="19" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>18</v>
       </c>
       <c r="B18" s="10">
         <v>1070.0353</v>
       </c>
-      <c r="C18" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C18" s="19" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
         <v>19</v>
       </c>
@@ -1088,39 +1099,39 @@
         <f>($B$8*$B$13)/B18</f>
         <v>91.036491973676007</v>
       </c>
-      <c r="C19" t="s">
-        <v>36</v>
-      </c>
-      <c r="G19" s="19" t="s">
+      <c r="C19" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="E19" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="M19" s="18" t="s">
+      <c r="K19" s="17" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="11">
         <v>150</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="19" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B21" s="12">
         <v>630.04870000000005</v>
       </c>
-      <c r="C21" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C21" s="19" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>22</v>
       </c>
@@ -1128,81 +1139,81 @@
         <f>($B$8*$B$13)/B21</f>
         <v>154.6106832694044</v>
       </c>
-      <c r="C22" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C22" s="19" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B23" s="13"/>
     </row>
-    <row r="24" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>24</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C24" s="17">
+      <c r="C24" s="20">
         <f>1/($B$8*0.01)</f>
         <v>2.4842868854495315E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C25" s="17">
+      <c r="C25" s="20">
         <f>2/($B$8*0.01)</f>
         <v>4.9685737708990631E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>26</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C26" s="17">
+      <c r="C26" s="20">
         <f>3/($B$8*0.01)</f>
         <v>7.452860656348595E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:13" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:13" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:13" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:13" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:13" ht="20.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G32" s="18" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="33" spans="7:7" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="7:7" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="7:7" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="7:7" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="7:7" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="7:7" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="7:7" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="7:7" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="7:7" ht="20.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G41" s="18" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="42" spans="7:7" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="7:7" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="7:7" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="7:7" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="7:7" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="7:7" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:11" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:11" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:11" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:11" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:11" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:11" ht="20.85" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E32" s="17" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="33" spans="5:5" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="5:5" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="5:5" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="5:5" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="5:5" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="5:5" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="5:5" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="5:5" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="5:5" ht="20.85" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E41" s="17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="42" spans="5:5" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="5:5" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="5:5" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="5:5" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="5:5" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="5:5" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
